--- a/figures/Figure2/data/experiments/experimental_basaltsCO2_extra_calculations.xlsx
+++ b/figures/Figure2/data/experiments/experimental_basaltsCO2_extra_calculations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="75">
   <si>
     <t>SiO2</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Citation</t>
   </si>
   <si>
-    <t>Reference Number</t>
-  </si>
-  <si>
     <t>Simplified Rock Type</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
   </si>
   <si>
     <t>Behrens et al 2009</t>
-  </si>
-  <si>
-    <t>waiting for #</t>
   </si>
   <si>
     <t>basalt</t>
@@ -602,10 +596,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:23">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,13 +666,10 @@
       <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" s="1" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="B2">
         <v>50.95</v>
@@ -717,42 +708,39 @@
         <v>0.0262</v>
       </c>
       <c r="N2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2">
-        <v>20</v>
-      </c>
-      <c r="P2" t="s">
-        <v>74</v>
+        <v>65</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2">
+        <v>1200</v>
       </c>
       <c r="Q2">
-        <v>1200</v>
+        <v>1950</v>
       </c>
       <c r="R2">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="S2">
-        <v>2000</v>
+        <v>2.18</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>0.5715624997474043</v>
       </c>
       <c r="U2">
-        <v>0.5715624997474043</v>
+        <v>0.3622215509955549</v>
       </c>
       <c r="V2">
-        <v>0.3622215509955549</v>
+        <v>0.5982366303550188</v>
       </c>
       <c r="W2">
-        <v>0.5982366303550188</v>
-      </c>
-      <c r="X2">
         <v>0.0365608248190747</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:23">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>50.17</v>
@@ -791,42 +779,39 @@
         <v>0.099</v>
       </c>
       <c r="N3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3">
-        <v>22</v>
-      </c>
-      <c r="P3" t="s">
-        <v>74</v>
+        <v>66</v>
+      </c>
+      <c r="O3" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3">
+        <v>1250</v>
       </c>
       <c r="Q3">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="R3">
         <v>2000</v>
       </c>
       <c r="S3">
-        <v>2000</v>
+        <v>2.56</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>0.4473992847472376</v>
       </c>
       <c r="U3">
-        <v>0.4473992847472376</v>
+        <v>-0.04006079292519527</v>
       </c>
       <c r="V3">
-        <v>-0.04006079292519527</v>
+        <v>0.593034957736338</v>
       </c>
       <c r="W3">
-        <v>0.593034957736338</v>
-      </c>
-      <c r="X3">
         <v>0.1395870740623374</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:23">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>50.17</v>
@@ -865,42 +850,39 @@
         <v>0.0598</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4">
-        <v>22</v>
-      </c>
-      <c r="P4" t="s">
-        <v>74</v>
+        <v>66</v>
+      </c>
+      <c r="O4" t="s">
+        <v>72</v>
+      </c>
+      <c r="P4">
+        <v>1250</v>
       </c>
       <c r="Q4">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="R4">
         <v>2000</v>
       </c>
       <c r="S4">
-        <v>2000</v>
+        <v>2.56</v>
       </c>
       <c r="T4">
-        <v>2.56</v>
+        <v>0.4473992847472376</v>
       </c>
       <c r="U4">
-        <v>0.4473992847472376</v>
+        <v>-0.03476691957047384</v>
       </c>
       <c r="V4">
-        <v>-0.03476691957047384</v>
+        <v>0.5839226087244054</v>
       </c>
       <c r="W4">
-        <v>0.5839226087244054</v>
-      </c>
-      <c r="X4">
         <v>0.07750034347129255</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:23">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>50.17</v>
@@ -939,42 +921,39 @@
         <v>0.0296</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5">
-        <v>22</v>
-      </c>
-      <c r="P5" t="s">
-        <v>74</v>
+        <v>66</v>
+      </c>
+      <c r="O5" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5">
+        <v>1250</v>
       </c>
       <c r="Q5">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="R5">
         <v>2000</v>
       </c>
       <c r="S5">
-        <v>2000</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>2.56</v>
+        <v>0.4473992847472376</v>
       </c>
       <c r="U5">
-        <v>0.4473992847472376</v>
+        <v>-0.03305542107934833</v>
       </c>
       <c r="V5">
-        <v>-0.03305542107934833</v>
+        <v>0.5806366750167452</v>
       </c>
       <c r="W5">
-        <v>0.5806366750167452</v>
-      </c>
-      <c r="X5">
         <v>0.0371871174094834</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:23">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>50.17</v>
@@ -1013,42 +992,39 @@
         <v>0.0195</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
-      </c>
-      <c r="O6">
-        <v>22</v>
-      </c>
-      <c r="P6" t="s">
-        <v>74</v>
+        <v>66</v>
+      </c>
+      <c r="O6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P6">
+        <v>1250</v>
       </c>
       <c r="Q6">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="R6">
         <v>2000</v>
       </c>
       <c r="S6">
-        <v>2000</v>
+        <v>2.56</v>
       </c>
       <c r="T6">
-        <v>2.56</v>
+        <v>0.4473992847472377</v>
       </c>
       <c r="U6">
-        <v>0.4473992847472377</v>
+        <v>-0.03270587618200915</v>
       </c>
       <c r="V6">
-        <v>-0.03270587618200915</v>
+        <v>0.5799514377816187</v>
       </c>
       <c r="W6">
-        <v>0.5799514377816187</v>
-      </c>
-      <c r="X6">
         <v>0.02433707657927474</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:23">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>50.17</v>
@@ -1087,42 +1063,39 @@
         <v>0.2183</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
-      </c>
-      <c r="O7">
-        <v>22</v>
-      </c>
-      <c r="P7" t="s">
-        <v>74</v>
+        <v>66</v>
+      </c>
+      <c r="O7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7">
+        <v>1250</v>
       </c>
       <c r="Q7">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="R7">
         <v>4000</v>
       </c>
       <c r="S7">
-        <v>4000</v>
+        <v>2.56</v>
       </c>
       <c r="T7">
-        <v>2.56</v>
+        <v>0.4473992847472377</v>
       </c>
       <c r="U7">
-        <v>0.4473992847472377</v>
+        <v>-0.0349608631242182</v>
       </c>
       <c r="V7">
-        <v>-0.0349608631242182</v>
+        <v>0.583714688231342</v>
       </c>
       <c r="W7">
-        <v>0.583714688231342</v>
-      </c>
-      <c r="X7">
         <v>0.2835892563971409</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:23">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>48.34</v>
@@ -1161,42 +1134,39 @@
         <v>0.1059</v>
       </c>
       <c r="N8" t="s">
-        <v>68</v>
-      </c>
-      <c r="O8">
-        <v>18</v>
-      </c>
-      <c r="P8" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O8" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8">
+        <v>1200</v>
       </c>
       <c r="Q8">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R8">
         <v>2000</v>
       </c>
       <c r="S8">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T8">
-        <v>2.9</v>
+        <v>0.5270406155106611</v>
       </c>
       <c r="U8">
-        <v>0.5270406155106611</v>
+        <v>0.4561894938088531</v>
       </c>
       <c r="V8">
-        <v>0.4561894938088531</v>
+        <v>0.6043296899837424</v>
       </c>
       <c r="W8">
-        <v>0.6043296899837424</v>
-      </c>
-      <c r="X8">
         <v>0.1500657092807335</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:23">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>48.34</v>
@@ -1235,42 +1205,39 @@
         <v>0.1061</v>
       </c>
       <c r="N9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O9">
-        <v>18</v>
-      </c>
-      <c r="P9" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O9" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9">
+        <v>1200</v>
       </c>
       <c r="Q9">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R9">
         <v>2000</v>
       </c>
       <c r="S9">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>0.5270406155106613</v>
       </c>
       <c r="U9">
-        <v>0.5270406155106613</v>
+        <v>0.4534410814869707</v>
       </c>
       <c r="V9">
-        <v>0.4534410814869707</v>
+        <v>0.6039146021148182</v>
       </c>
       <c r="W9">
-        <v>0.6039146021148182</v>
-      </c>
-      <c r="X9">
         <v>0.1498301559904437</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:23">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10">
         <v>48.34</v>
@@ -1309,42 +1276,39 @@
         <v>0.1006</v>
       </c>
       <c r="N10" t="s">
-        <v>68</v>
-      </c>
-      <c r="O10">
-        <v>18</v>
-      </c>
-      <c r="P10" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O10" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10">
+        <v>1200</v>
       </c>
       <c r="Q10">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R10">
         <v>2000</v>
       </c>
       <c r="S10">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T10">
-        <v>2.9</v>
+        <v>0.5270406155106611</v>
       </c>
       <c r="U10">
-        <v>0.5270406155106611</v>
+        <v>0.4502180199823069</v>
       </c>
       <c r="V10">
-        <v>0.4502180199823069</v>
+        <v>0.6034475508180359</v>
       </c>
       <c r="W10">
-        <v>0.6034475508180359</v>
-      </c>
-      <c r="X10">
         <v>0.1414886901037698</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:23">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <v>48.34</v>
@@ -1383,42 +1347,39 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="N11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O11">
-        <v>18</v>
-      </c>
-      <c r="P11" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O11" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11">
+        <v>1200</v>
       </c>
       <c r="Q11">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R11">
         <v>2000</v>
       </c>
       <c r="S11">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>0.5270406155106609</v>
       </c>
       <c r="U11">
-        <v>0.5270406155106609</v>
+        <v>0.4494283254955933</v>
       </c>
       <c r="V11">
-        <v>0.4494283254955933</v>
+        <v>0.6033392849826194</v>
       </c>
       <c r="W11">
-        <v>0.6033392849826194</v>
-      </c>
-      <c r="X11">
         <v>0.1371338173052426</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:23">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>48.34</v>
@@ -1457,42 +1418,39 @@
         <v>0.1033</v>
       </c>
       <c r="N12" t="s">
-        <v>68</v>
-      </c>
-      <c r="O12">
-        <v>18</v>
-      </c>
-      <c r="P12" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O12" t="s">
+        <v>72</v>
+      </c>
+      <c r="P12">
+        <v>1200</v>
       </c>
       <c r="Q12">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R12">
         <v>2000</v>
       </c>
       <c r="S12">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>0.5270406155106611</v>
       </c>
       <c r="U12">
-        <v>0.5270406155106611</v>
+        <v>0.444883009279768</v>
       </c>
       <c r="V12">
-        <v>0.444883009279768</v>
+        <v>0.6026147359509771</v>
       </c>
       <c r="W12">
-        <v>0.6026147359509771</v>
-      </c>
-      <c r="X12">
         <v>0.1442893677006401</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:23">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>48.34</v>
@@ -1531,42 +1489,39 @@
         <v>0.0794</v>
       </c>
       <c r="N13" t="s">
-        <v>68</v>
-      </c>
-      <c r="O13">
-        <v>18</v>
-      </c>
-      <c r="P13" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P13">
+        <v>1200</v>
       </c>
       <c r="Q13">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R13">
         <v>2000</v>
       </c>
       <c r="S13">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>0.5270406155106611</v>
       </c>
       <c r="U13">
-        <v>0.5270406155106611</v>
+        <v>0.4270896528015311</v>
       </c>
       <c r="V13">
-        <v>0.4270896528015311</v>
+        <v>0.5998754477309302</v>
       </c>
       <c r="W13">
-        <v>0.5998754477309302</v>
-      </c>
-      <c r="X13">
         <v>0.1083184623588433</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:23">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14">
         <v>48.34</v>
@@ -1605,42 +1560,39 @@
         <v>0.0992</v>
       </c>
       <c r="N14" t="s">
-        <v>68</v>
-      </c>
-      <c r="O14">
-        <v>18</v>
-      </c>
-      <c r="P14" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O14" t="s">
+        <v>72</v>
+      </c>
+      <c r="P14">
+        <v>1200</v>
       </c>
       <c r="Q14">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R14">
         <v>2000</v>
       </c>
       <c r="S14">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T14">
-        <v>2.9</v>
+        <v>0.5270406155106612</v>
       </c>
       <c r="U14">
-        <v>0.5270406155106612</v>
+        <v>0.4233899288461607</v>
       </c>
       <c r="V14">
-        <v>0.4233899288461607</v>
+        <v>0.5991857497948737</v>
       </c>
       <c r="W14">
-        <v>0.5991857497948737</v>
-      </c>
-      <c r="X14">
         <v>0.1346207110117405</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:23">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>48.34</v>
@@ -1679,42 +1631,39 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="N15" t="s">
-        <v>68</v>
-      </c>
-      <c r="O15">
-        <v>18</v>
-      </c>
-      <c r="P15" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O15" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15">
+        <v>1200</v>
       </c>
       <c r="Q15">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R15">
         <v>2000</v>
       </c>
       <c r="S15">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T15">
-        <v>2.9</v>
+        <v>0.5270406155106611</v>
       </c>
       <c r="U15">
-        <v>0.5270406155106611</v>
+        <v>0.4134918735877089</v>
       </c>
       <c r="V15">
-        <v>0.4134918735877089</v>
+        <v>0.5976051445642688</v>
       </c>
       <c r="W15">
-        <v>0.5976051445642688</v>
-      </c>
-      <c r="X15">
         <v>0.1046606147608195</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:23">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16">
         <v>48.34</v>
@@ -1753,42 +1702,39 @@
         <v>0.0814</v>
       </c>
       <c r="N16" t="s">
-        <v>68</v>
-      </c>
-      <c r="O16">
-        <v>18</v>
-      </c>
-      <c r="P16" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="O16" t="s">
+        <v>72</v>
+      </c>
+      <c r="P16">
+        <v>1200</v>
       </c>
       <c r="Q16">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R16">
         <v>2000</v>
       </c>
       <c r="S16">
-        <v>2000</v>
+        <v>2.9</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>0.5270406155106611</v>
       </c>
       <c r="U16">
-        <v>0.5270406155106611</v>
+        <v>0.4030736859866413</v>
       </c>
       <c r="V16">
-        <v>0.4030736859866413</v>
+        <v>0.5957832715767141</v>
       </c>
       <c r="W16">
-        <v>0.5957832715767141</v>
-      </c>
-      <c r="X16">
         <v>0.1072905219651995</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:23">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17">
         <v>49.07</v>
@@ -1827,42 +1773,39 @@
         <v>0.2</v>
       </c>
       <c r="N17" t="s">
-        <v>69</v>
-      </c>
-      <c r="O17">
-        <v>19</v>
-      </c>
-      <c r="P17" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="O17" t="s">
+        <v>72</v>
+      </c>
+      <c r="P17">
+        <v>1150</v>
       </c>
       <c r="Q17">
-        <v>1150</v>
+        <v>2130</v>
       </c>
       <c r="R17">
-        <v>2130</v>
+        <v>2000</v>
       </c>
       <c r="S17">
-        <v>2000</v>
+        <v>4.04</v>
       </c>
       <c r="T17">
-        <v>4.04</v>
+        <v>0.6779242353325791</v>
       </c>
       <c r="U17">
-        <v>0.6779242353325791</v>
+        <v>1.169635561604286</v>
       </c>
       <c r="V17">
-        <v>1.169635561604286</v>
+        <v>0.5969598114317275</v>
       </c>
       <c r="W17">
-        <v>0.5969598114317275</v>
-      </c>
-      <c r="X17">
         <v>0.2595199388459163</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:23">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18">
         <v>49.18</v>
@@ -1901,42 +1844,39 @@
         <v>0.2</v>
       </c>
       <c r="N18" t="s">
-        <v>69</v>
-      </c>
-      <c r="O18">
-        <v>19</v>
-      </c>
-      <c r="P18" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="O18" t="s">
+        <v>72</v>
+      </c>
+      <c r="P18">
+        <v>1100</v>
       </c>
       <c r="Q18">
-        <v>1100</v>
+        <v>2140</v>
       </c>
       <c r="R18">
-        <v>2140</v>
+        <v>2000</v>
       </c>
       <c r="S18">
-        <v>2000</v>
+        <v>4.09</v>
       </c>
       <c r="T18">
-        <v>4.09</v>
+        <v>0.6726467633352319</v>
       </c>
       <c r="U18">
-        <v>0.6726467633352319</v>
+        <v>1.124844997303982</v>
       </c>
       <c r="V18">
-        <v>1.124844997303982</v>
+        <v>0.5965705576063646</v>
       </c>
       <c r="W18">
-        <v>0.5965705576063646</v>
-      </c>
-      <c r="X18">
         <v>0.259578493557037</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:23">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19">
         <v>49.4</v>
@@ -1975,42 +1915,39 @@
         <v>0.117</v>
       </c>
       <c r="N19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O19" t="s">
-        <v>73</v>
-      </c>
-      <c r="P19" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="P19">
+        <v>1200</v>
       </c>
       <c r="Q19">
-        <v>1200</v>
+        <v>2059</v>
       </c>
       <c r="R19">
-        <v>2059</v>
+        <v>2000</v>
       </c>
       <c r="S19">
-        <v>2000</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="T19">
-        <v>4.199999999999999</v>
+        <v>0.5932505378449908</v>
       </c>
       <c r="U19">
-        <v>0.5932505378449908</v>
+        <v>0.6935581304665317</v>
       </c>
       <c r="V19">
-        <v>0.6935581304665317</v>
+        <v>0.5958032079463255</v>
       </c>
       <c r="W19">
-        <v>0.5958032079463255</v>
-      </c>
-      <c r="X19">
         <v>0.1592940032384997</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:23">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20">
         <v>48.13</v>
@@ -2049,42 +1986,39 @@
         <v>0.6086</v>
       </c>
       <c r="N20" t="s">
-        <v>71</v>
-      </c>
-      <c r="O20">
-        <v>16</v>
-      </c>
-      <c r="P20" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="O20" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20">
+        <v>1200</v>
       </c>
       <c r="Q20">
-        <v>1200</v>
+        <v>6098</v>
       </c>
       <c r="R20">
-        <v>6098</v>
+        <v>6000</v>
       </c>
       <c r="S20">
-        <v>6000</v>
+        <v>4.28</v>
       </c>
       <c r="T20">
-        <v>4.28</v>
+        <v>0.5539868738682118</v>
       </c>
       <c r="U20">
-        <v>0.5539868738682118</v>
+        <v>0.4333203164114683</v>
       </c>
       <c r="V20">
-        <v>0.4333203164114683</v>
+        <v>0.5863930355951317</v>
       </c>
       <c r="W20">
-        <v>0.5863930355951317</v>
-      </c>
-      <c r="X20">
         <v>0.755338589830322</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:23">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21">
         <v>48.21</v>
@@ -2123,42 +2057,39 @@
         <v>0.3176</v>
       </c>
       <c r="N21" t="s">
-        <v>71</v>
-      </c>
-      <c r="O21">
-        <v>16</v>
-      </c>
-      <c r="P21" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="O21" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21">
+        <v>1200</v>
       </c>
       <c r="Q21">
-        <v>1200</v>
+        <v>4071</v>
       </c>
       <c r="R21">
-        <v>4071</v>
+        <v>4000</v>
       </c>
       <c r="S21">
-        <v>4000</v>
+        <v>4.28</v>
       </c>
       <c r="T21">
-        <v>4.28</v>
+        <v>0.5525962776301148</v>
       </c>
       <c r="U21">
-        <v>0.5525962776301148</v>
+        <v>0.4710687959175628</v>
       </c>
       <c r="V21">
-        <v>0.4710687959175628</v>
+        <v>0.593307108343605</v>
       </c>
       <c r="W21">
-        <v>0.593307108343605</v>
-      </c>
-      <c r="X21">
         <v>0.4148136123031654</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:23">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22">
         <v>49.81</v>
@@ -2197,42 +2128,39 @@
         <v>0.6086</v>
       </c>
       <c r="N22" t="s">
-        <v>71</v>
-      </c>
-      <c r="O22">
-        <v>16</v>
-      </c>
-      <c r="P22" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="O22" t="s">
+        <v>72</v>
+      </c>
+      <c r="P22">
+        <v>1200</v>
       </c>
       <c r="Q22">
-        <v>1200</v>
+        <v>6080</v>
       </c>
       <c r="R22">
-        <v>6080</v>
+        <v>6000</v>
       </c>
       <c r="S22">
-        <v>6000</v>
+        <v>4.3</v>
       </c>
       <c r="T22">
-        <v>4.3</v>
+        <v>0.5813739888505197</v>
       </c>
       <c r="U22">
-        <v>0.5813739888505197</v>
+        <v>0.5384396626613648</v>
       </c>
       <c r="V22">
-        <v>0.5384396626613648</v>
+        <v>0.5835966569854208</v>
       </c>
       <c r="W22">
-        <v>0.5835966569854208</v>
-      </c>
-      <c r="X22">
         <v>0.752416038169434</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:23">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23">
         <v>50.26</v>
@@ -2271,42 +2199,39 @@
         <v>0.13</v>
       </c>
       <c r="N23" t="s">
-        <v>69</v>
-      </c>
-      <c r="O23">
-        <v>19</v>
-      </c>
-      <c r="P23" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="O23" t="s">
+        <v>72</v>
+      </c>
+      <c r="P23">
+        <v>1150</v>
       </c>
       <c r="Q23">
-        <v>1150</v>
+        <v>2130</v>
       </c>
       <c r="R23">
-        <v>2130</v>
+        <v>2000</v>
       </c>
       <c r="S23">
-        <v>2000</v>
+        <v>4.359999999999999</v>
       </c>
       <c r="T23">
-        <v>4.359999999999999</v>
+        <v>0.5778840656124614</v>
       </c>
       <c r="U23">
-        <v>0.5778840656124614</v>
+        <v>0.7194434644740286</v>
       </c>
       <c r="V23">
-        <v>0.7194434644740286</v>
+        <v>0.591827435211803</v>
       </c>
       <c r="W23">
-        <v>0.591827435211803</v>
-      </c>
-      <c r="X23">
         <v>0.1711753959401769</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:23">
       <c r="A24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24">
         <v>47.76</v>
@@ -2345,42 +2270,39 @@
         <v>0.28</v>
       </c>
       <c r="N24" t="s">
-        <v>69</v>
-      </c>
-      <c r="O24">
-        <v>19</v>
-      </c>
-      <c r="P24" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="O24" t="s">
+        <v>72</v>
+      </c>
+      <c r="P24">
+        <v>1150</v>
       </c>
       <c r="Q24">
-        <v>1150</v>
+        <v>2130</v>
       </c>
       <c r="R24">
-        <v>2130</v>
+        <v>2000</v>
       </c>
       <c r="S24">
-        <v>2000</v>
+        <v>4.45</v>
       </c>
       <c r="T24">
-        <v>4.45</v>
+        <v>0.6959612508386809</v>
       </c>
       <c r="U24">
-        <v>0.6959612508386809</v>
+        <v>1.463918034076054</v>
       </c>
       <c r="V24">
-        <v>1.463918034076054</v>
+        <v>0.6022549015433586</v>
       </c>
       <c r="W24">
-        <v>0.6022549015433586</v>
-      </c>
-      <c r="X24">
         <v>0.3659907338205871</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:23">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>50.03</v>
@@ -2419,42 +2341,39 @@
         <v>0.3568</v>
       </c>
       <c r="N25" t="s">
-        <v>71</v>
-      </c>
-      <c r="O25">
-        <v>16</v>
-      </c>
-      <c r="P25" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="O25" t="s">
+        <v>72</v>
+      </c>
+      <c r="P25">
+        <v>1200</v>
       </c>
       <c r="Q25">
-        <v>1200</v>
+        <v>4270</v>
       </c>
       <c r="R25">
-        <v>4270</v>
+        <v>4000</v>
       </c>
       <c r="S25">
-        <v>4000</v>
+        <v>4.45</v>
       </c>
       <c r="T25">
-        <v>4.45</v>
+        <v>0.5721697073140337</v>
       </c>
       <c r="U25">
-        <v>0.5721697073140337</v>
+        <v>0.5667815144723662</v>
       </c>
       <c r="V25">
-        <v>0.5667815144723662</v>
+        <v>0.5902799556031445</v>
       </c>
       <c r="W25">
-        <v>0.5902799556031445</v>
-      </c>
-      <c r="X25">
         <v>0.4689538541217309</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:23">
       <c r="A26" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26">
         <v>53.12</v>
@@ -2493,42 +2412,39 @@
         <v>0.4963</v>
       </c>
       <c r="N26" t="s">
-        <v>71</v>
-      </c>
-      <c r="O26">
-        <v>16</v>
-      </c>
-      <c r="P26" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="O26" t="s">
+        <v>73</v>
+      </c>
+      <c r="P26">
+        <v>1200</v>
       </c>
       <c r="Q26">
-        <v>1200</v>
+        <v>6123</v>
       </c>
       <c r="R26">
-        <v>6123</v>
+        <v>6000</v>
       </c>
       <c r="S26">
-        <v>6000</v>
+        <v>4.53</v>
       </c>
       <c r="T26">
-        <v>4.53</v>
+        <v>0.4141666498520744</v>
       </c>
       <c r="U26">
-        <v>0.4141666498520744</v>
+        <v>-0.1653993696156948</v>
       </c>
       <c r="V26">
-        <v>-0.1653993696156948</v>
+        <v>0.5695956094576333</v>
       </c>
       <c r="W26">
-        <v>0.5695956094576333</v>
-      </c>
-      <c r="X26">
         <v>0.6093791090942784</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:23">
       <c r="A27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27">
         <v>52.63</v>
@@ -2567,42 +2483,39 @@
         <v>0.3049</v>
       </c>
       <c r="N27" t="s">
-        <v>71</v>
-      </c>
-      <c r="O27">
-        <v>16</v>
-      </c>
-      <c r="P27" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="O27" t="s">
+        <v>73</v>
+      </c>
+      <c r="P27">
+        <v>1200</v>
       </c>
       <c r="Q27">
-        <v>1200</v>
+        <v>4255</v>
       </c>
       <c r="R27">
-        <v>4255</v>
+        <v>4000</v>
       </c>
       <c r="S27">
-        <v>4000</v>
+        <v>4.71</v>
       </c>
       <c r="T27">
-        <v>4.71</v>
+        <v>0.3929833674560731</v>
       </c>
       <c r="U27">
-        <v>0.3929833674560731</v>
+        <v>-0.1845260634609778</v>
       </c>
       <c r="V27">
-        <v>-0.1845260634609778</v>
+        <v>0.578340104747631</v>
       </c>
       <c r="W27">
-        <v>0.578340104747631</v>
-      </c>
-      <c r="X27">
         <v>0.4061836479247533</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:23">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28">
         <v>52.82</v>
@@ -2641,42 +2554,39 @@
         <v>0.552</v>
       </c>
       <c r="N28" t="s">
-        <v>71</v>
-      </c>
-      <c r="O28">
-        <v>16</v>
-      </c>
-      <c r="P28" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="O28" t="s">
+        <v>73</v>
+      </c>
+      <c r="P28">
+        <v>1200</v>
       </c>
       <c r="Q28">
-        <v>1200</v>
+        <v>6141</v>
       </c>
       <c r="R28">
-        <v>6141</v>
+        <v>6000</v>
       </c>
       <c r="S28">
-        <v>6000</v>
+        <v>4.779999999999999</v>
       </c>
       <c r="T28">
-        <v>4.779999999999999</v>
+        <v>0.3790283840888591</v>
       </c>
       <c r="U28">
-        <v>0.3790283840888591</v>
+        <v>-0.2192520212932023</v>
       </c>
       <c r="V28">
-        <v>-0.2192520212932023</v>
+        <v>0.5715081016960706</v>
       </c>
       <c r="W28">
-        <v>0.5715081016960706</v>
-      </c>
-      <c r="X28">
         <v>0.6997114039606604</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:23">
       <c r="A29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29">
         <v>47.59</v>
@@ -2715,42 +2625,39 @@
         <v>0.1429</v>
       </c>
       <c r="N29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O29" t="s">
-        <v>73</v>
-      </c>
-      <c r="P29" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="P29">
+        <v>1200</v>
       </c>
       <c r="Q29">
-        <v>1200</v>
+        <v>2059</v>
       </c>
       <c r="R29">
-        <v>2059</v>
+        <v>2000</v>
       </c>
       <c r="S29">
-        <v>2000</v>
+        <v>5.4</v>
       </c>
       <c r="T29">
-        <v>5.4</v>
+        <v>0.4664922714257458</v>
       </c>
       <c r="U29">
-        <v>0.4664922714257458</v>
+        <v>0.5543834984041034</v>
       </c>
       <c r="V29">
-        <v>0.5543834984041034</v>
+        <v>0.5997916385628772</v>
       </c>
       <c r="W29">
-        <v>0.5997916385628772</v>
-      </c>
-      <c r="X29">
         <v>0.1999551058878538</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:23">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30">
         <v>48.77</v>
@@ -2789,42 +2696,39 @@
         <v>0.3996</v>
       </c>
       <c r="N30" t="s">
-        <v>71</v>
-      </c>
-      <c r="O30">
-        <v>16</v>
-      </c>
-      <c r="P30" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O30" t="s">
+        <v>74</v>
+      </c>
+      <c r="P30">
+        <v>1200</v>
       </c>
       <c r="Q30">
-        <v>1200</v>
+        <v>4041</v>
       </c>
       <c r="R30">
-        <v>4041</v>
+        <v>4000</v>
       </c>
       <c r="S30">
-        <v>4000</v>
+        <v>5.44</v>
       </c>
       <c r="T30">
-        <v>5.44</v>
+        <v>0.4956109595594793</v>
       </c>
       <c r="U30">
-        <v>0.4956109595594793</v>
+        <v>0.5330951017812051</v>
       </c>
       <c r="V30">
-        <v>0.5330951017812051</v>
+        <v>0.5921766788436884</v>
       </c>
       <c r="W30">
-        <v>0.5921766788436884</v>
-      </c>
-      <c r="X30">
         <v>0.5274103122846289</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:23">
       <c r="A31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31">
         <v>48.91</v>
@@ -2863,42 +2767,39 @@
         <v>0.7072000000000001</v>
       </c>
       <c r="N31" t="s">
-        <v>71</v>
-      </c>
-      <c r="O31">
-        <v>16</v>
-      </c>
-      <c r="P31" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O31" t="s">
+        <v>74</v>
+      </c>
+      <c r="P31">
+        <v>1200</v>
       </c>
       <c r="Q31">
-        <v>1200</v>
+        <v>6168</v>
       </c>
       <c r="R31">
-        <v>6168</v>
+        <v>6000</v>
       </c>
       <c r="S31">
-        <v>6000</v>
+        <v>5.45</v>
       </c>
       <c r="T31">
-        <v>5.45</v>
+        <v>0.49479942437638</v>
       </c>
       <c r="U31">
-        <v>0.49479942437638</v>
+        <v>0.455568312564854</v>
       </c>
       <c r="V31">
-        <v>0.455568312564854</v>
+        <v>0.5817408722901297</v>
       </c>
       <c r="W31">
-        <v>0.5817408722901297</v>
-      </c>
-      <c r="X31">
         <v>0.8599388012590624</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:23">
       <c r="A32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B32">
         <v>49.06</v>
@@ -2937,42 +2838,39 @@
         <v>0.7659</v>
       </c>
       <c r="N32" t="s">
-        <v>71</v>
-      </c>
-      <c r="O32">
-        <v>16</v>
-      </c>
-      <c r="P32" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O32" t="s">
+        <v>74</v>
+      </c>
+      <c r="P32">
+        <v>1200</v>
       </c>
       <c r="Q32">
-        <v>1200</v>
+        <v>6199</v>
       </c>
       <c r="R32">
-        <v>6199</v>
+        <v>6000</v>
       </c>
       <c r="S32">
-        <v>6000</v>
+        <v>5.5</v>
       </c>
       <c r="T32">
-        <v>5.5</v>
+        <v>0.5155029625644975</v>
       </c>
       <c r="U32">
-        <v>0.5155029625644975</v>
+        <v>0.4874834790919516</v>
       </c>
       <c r="V32">
-        <v>0.4874834790919516</v>
+        <v>0.5855432925968794</v>
       </c>
       <c r="W32">
-        <v>0.5855432925968794</v>
-      </c>
-      <c r="X32">
         <v>0.9471890902024246</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:23">
       <c r="A33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33">
         <v>48.8</v>
@@ -3011,42 +2909,39 @@
         <v>0.4426</v>
       </c>
       <c r="N33" t="s">
-        <v>71</v>
-      </c>
-      <c r="O33">
-        <v>16</v>
-      </c>
-      <c r="P33" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O33" t="s">
+        <v>74</v>
+      </c>
+      <c r="P33">
+        <v>1200</v>
       </c>
       <c r="Q33">
-        <v>1200</v>
+        <v>4194</v>
       </c>
       <c r="R33">
-        <v>4194</v>
+        <v>4000</v>
       </c>
       <c r="S33">
-        <v>4000</v>
+        <v>5.62</v>
       </c>
       <c r="T33">
-        <v>5.62</v>
+        <v>0.517560898754001</v>
       </c>
       <c r="U33">
-        <v>0.517560898754001</v>
+        <v>0.5465561622161297</v>
       </c>
       <c r="V33">
-        <v>0.5465561622161297</v>
+        <v>0.5917905688306624</v>
       </c>
       <c r="W33">
-        <v>0.5917905688306624</v>
-      </c>
-      <c r="X33">
         <v>0.5701573291885853</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:23">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34">
         <v>48.02</v>
@@ -3085,42 +2980,39 @@
         <v>0.2094</v>
       </c>
       <c r="N34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O34" t="s">
-        <v>73</v>
-      </c>
-      <c r="P34" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="P34">
+        <v>1200</v>
       </c>
       <c r="Q34">
-        <v>1200</v>
+        <v>2059</v>
       </c>
       <c r="R34">
-        <v>2059</v>
+        <v>2000</v>
       </c>
       <c r="S34">
-        <v>2000</v>
+        <v>7.35</v>
       </c>
       <c r="T34">
-        <v>7.35</v>
+        <v>0.6299131534865419</v>
       </c>
       <c r="U34">
-        <v>0.6299131534865419</v>
+        <v>1.320268500922855</v>
       </c>
       <c r="V34">
-        <v>1.320268500922855</v>
+        <v>0.6074910015767786</v>
       </c>
       <c r="W34">
-        <v>0.6074910015767786</v>
-      </c>
-      <c r="X34">
         <v>0.297968074458911</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:23">
       <c r="A35" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <v>49.37</v>
@@ -3159,42 +3051,39 @@
         <v>0.9542</v>
       </c>
       <c r="N35" t="s">
-        <v>71</v>
-      </c>
-      <c r="O35">
-        <v>16</v>
-      </c>
-      <c r="P35" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O35" t="s">
+        <v>74</v>
+      </c>
+      <c r="P35">
+        <v>1200</v>
       </c>
       <c r="Q35">
-        <v>1200</v>
+        <v>6221</v>
       </c>
       <c r="R35">
-        <v>6221</v>
+        <v>6000</v>
       </c>
       <c r="S35">
-        <v>6000</v>
+        <v>7.83</v>
       </c>
       <c r="T35">
-        <v>7.83</v>
+        <v>0.5754130011071131</v>
       </c>
       <c r="U35">
-        <v>0.5754130011071131</v>
+        <v>0.8353342801679426</v>
       </c>
       <c r="V35">
-        <v>0.8353342801679426</v>
+        <v>0.5859228530439567</v>
       </c>
       <c r="W35">
-        <v>0.5859228530439567</v>
-      </c>
-      <c r="X35">
         <v>1.178681494908291</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:23">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36">
         <v>49.2</v>
@@ -3233,42 +3122,39 @@
         <v>0.4963</v>
       </c>
       <c r="N36" t="s">
-        <v>71</v>
-      </c>
-      <c r="O36">
-        <v>16</v>
-      </c>
-      <c r="P36" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O36" t="s">
+        <v>74</v>
+      </c>
+      <c r="P36">
+        <v>1200</v>
       </c>
       <c r="Q36">
-        <v>1200</v>
+        <v>4127</v>
       </c>
       <c r="R36">
-        <v>4127</v>
+        <v>4000</v>
       </c>
       <c r="S36">
-        <v>4000</v>
+        <v>7.869999999999999</v>
       </c>
       <c r="T36">
-        <v>7.869999999999999</v>
+        <v>0.578139952994535</v>
       </c>
       <c r="U36">
-        <v>0.578139952994535</v>
+        <v>0.9060067375517149</v>
       </c>
       <c r="V36">
-        <v>0.9060067375517149</v>
+        <v>0.5925646158806936</v>
       </c>
       <c r="W36">
-        <v>0.5925646158806936</v>
-      </c>
-      <c r="X36">
         <v>0.6398014462025452</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:23">
       <c r="A37" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37">
         <v>49.11</v>
@@ -3307,42 +3193,39 @@
         <v>0.8501</v>
       </c>
       <c r="N37" t="s">
-        <v>71</v>
-      </c>
-      <c r="O37">
-        <v>16</v>
-      </c>
-      <c r="P37" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O37" t="s">
+        <v>74</v>
+      </c>
+      <c r="P37">
+        <v>1200</v>
       </c>
       <c r="Q37">
-        <v>1200</v>
+        <v>6077</v>
       </c>
       <c r="R37">
-        <v>6077</v>
+        <v>6000</v>
       </c>
       <c r="S37">
-        <v>6000</v>
+        <v>7.899999999999999</v>
       </c>
       <c r="T37">
-        <v>7.899999999999999</v>
+        <v>0.583593913711922</v>
       </c>
       <c r="U37">
-        <v>0.583593913711922</v>
+        <v>0.9112519488258686</v>
       </c>
       <c r="V37">
-        <v>0.9112519488258686</v>
+        <v>0.589586336707862</v>
       </c>
       <c r="W37">
-        <v>0.589586336707862</v>
-      </c>
-      <c r="X37">
         <v>1.073177897374676</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:23">
       <c r="A38" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38">
         <v>48.61</v>
@@ -3381,42 +3264,39 @@
         <v>0.6754</v>
       </c>
       <c r="N38" t="s">
-        <v>71</v>
-      </c>
-      <c r="O38">
-        <v>16</v>
-      </c>
-      <c r="P38" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O38" t="s">
+        <v>74</v>
+      </c>
+      <c r="P38">
+        <v>1200</v>
       </c>
       <c r="Q38">
-        <v>1200</v>
+        <v>6175</v>
       </c>
       <c r="R38">
-        <v>6175</v>
+        <v>6000</v>
       </c>
       <c r="S38">
-        <v>6000</v>
+        <v>9.16</v>
       </c>
       <c r="T38">
-        <v>9.16</v>
+        <v>0.2608473260653944</v>
       </c>
       <c r="U38">
-        <v>0.2608473260653944</v>
+        <v>0.07184218827082933</v>
       </c>
       <c r="V38">
-        <v>0.07184218827082933</v>
+        <v>0.5869242829937442</v>
       </c>
       <c r="W38">
-        <v>0.5869242829937442</v>
-      </c>
-      <c r="X38">
         <v>0.9410662245651471</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:23">
       <c r="A39" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B39">
         <v>49.89</v>
@@ -3455,42 +3335,39 @@
         <v>0.265</v>
       </c>
       <c r="N39" t="s">
-        <v>72</v>
-      </c>
-      <c r="O39">
-        <v>17</v>
-      </c>
-      <c r="P39" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="O39" t="s">
+        <v>74</v>
+      </c>
+      <c r="P39">
+        <v>1250</v>
       </c>
       <c r="Q39">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="R39">
         <v>2000</v>
       </c>
       <c r="S39">
-        <v>2000</v>
+        <v>9.67</v>
       </c>
       <c r="T39">
-        <v>9.67</v>
+        <v>0.5751061917811177</v>
       </c>
       <c r="U39">
-        <v>0.5751061917811177</v>
+        <v>1.147934935924553</v>
       </c>
       <c r="V39">
-        <v>1.147934935924553</v>
+        <v>0.6066655915779244</v>
       </c>
       <c r="W39">
-        <v>0.6066655915779244</v>
-      </c>
-      <c r="X39">
         <v>0.366157392696854</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:23">
       <c r="A40" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40">
         <v>49.89</v>
@@ -3529,42 +3406,39 @@
         <v>0.364</v>
       </c>
       <c r="N40" t="s">
-        <v>72</v>
-      </c>
-      <c r="O40">
-        <v>17</v>
-      </c>
-      <c r="P40" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="O40" t="s">
+        <v>74</v>
+      </c>
+      <c r="P40">
+        <v>1200</v>
       </c>
       <c r="Q40">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R40">
         <v>2000</v>
       </c>
       <c r="S40">
-        <v>2000</v>
+        <v>9.67</v>
       </c>
       <c r="T40">
-        <v>9.67</v>
+        <v>0.5751061917811177</v>
       </c>
       <c r="U40">
-        <v>0.5751061917811177</v>
+        <v>1.144082789203735</v>
       </c>
       <c r="V40">
-        <v>1.144082789203735</v>
+        <v>0.6060099742650306</v>
       </c>
       <c r="W40">
-        <v>0.6060099742650306</v>
-      </c>
-      <c r="X40">
         <v>0.5015850913535289</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:23">
       <c r="A41" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41">
         <v>49.89</v>
@@ -3603,42 +3477,39 @@
         <v>0.287</v>
       </c>
       <c r="N41" t="s">
-        <v>72</v>
-      </c>
-      <c r="O41">
-        <v>17</v>
-      </c>
-      <c r="P41" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="O41" t="s">
+        <v>74</v>
+      </c>
+      <c r="P41">
+        <v>1200</v>
       </c>
       <c r="Q41">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R41">
         <v>2000</v>
       </c>
       <c r="S41">
-        <v>2000</v>
+        <v>9.67</v>
       </c>
       <c r="T41">
-        <v>9.67</v>
+        <v>0.5751061917811175</v>
       </c>
       <c r="U41">
-        <v>0.5751061917811175</v>
+        <v>1.134967782628241</v>
       </c>
       <c r="V41">
-        <v>1.134967782628241</v>
+        <v>0.6057400414577302</v>
       </c>
       <c r="W41">
-        <v>0.6057400414577302</v>
-      </c>
-      <c r="X41">
         <v>0.3937780010846086</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:23">
       <c r="A42" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B42">
         <v>49.89</v>
@@ -3677,42 +3548,39 @@
         <v>0.303</v>
       </c>
       <c r="N42" t="s">
-        <v>72</v>
-      </c>
-      <c r="O42">
-        <v>17</v>
-      </c>
-      <c r="P42" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="O42" t="s">
+        <v>74</v>
+      </c>
+      <c r="P42">
+        <v>1200</v>
       </c>
       <c r="Q42">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R42">
         <v>2000</v>
       </c>
       <c r="S42">
-        <v>2000</v>
+        <v>9.67</v>
       </c>
       <c r="T42">
-        <v>9.67</v>
+        <v>0.5751061917811175</v>
       </c>
       <c r="U42">
-        <v>0.5751061917811175</v>
+        <v>1.11023669819319</v>
       </c>
       <c r="V42">
-        <v>1.11023669819319</v>
+        <v>0.6040491809603067</v>
       </c>
       <c r="W42">
-        <v>0.6040491809603067</v>
-      </c>
-      <c r="X42">
         <v>0.4101432881146098</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:23">
       <c r="A43" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43">
         <v>49.89</v>
@@ -3751,42 +3619,39 @@
         <v>0.276</v>
       </c>
       <c r="N43" t="s">
-        <v>72</v>
-      </c>
-      <c r="O43">
-        <v>17</v>
-      </c>
-      <c r="P43" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="O43" t="s">
+        <v>74</v>
+      </c>
+      <c r="P43">
+        <v>1200</v>
       </c>
       <c r="Q43">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R43">
         <v>2000</v>
       </c>
       <c r="S43">
-        <v>2000</v>
+        <v>9.67</v>
       </c>
       <c r="T43">
-        <v>9.67</v>
+        <v>0.5751061917811175</v>
       </c>
       <c r="U43">
-        <v>0.5751061917811175</v>
+        <v>1.07008259364732</v>
       </c>
       <c r="V43">
-        <v>1.07008259364732</v>
+        <v>0.6014173823380048</v>
       </c>
       <c r="W43">
-        <v>0.6014173823380048</v>
-      </c>
-      <c r="X43">
         <v>0.3652763977282621</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:23">
       <c r="A44" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B44">
         <v>49.89</v>
@@ -3825,36 +3690,33 @@
         <v>0.257</v>
       </c>
       <c r="N44" t="s">
-        <v>72</v>
-      </c>
-      <c r="O44">
-        <v>17</v>
-      </c>
-      <c r="P44" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="O44" t="s">
+        <v>74</v>
+      </c>
+      <c r="P44">
+        <v>1200</v>
       </c>
       <c r="Q44">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="R44">
         <v>2000</v>
       </c>
       <c r="S44">
-        <v>2000</v>
+        <v>9.67</v>
       </c>
       <c r="T44">
-        <v>9.67</v>
+        <v>0.5751061917811177</v>
       </c>
       <c r="U44">
-        <v>0.5751061917811177</v>
+        <v>1.064201738434421</v>
       </c>
       <c r="V44">
-        <v>1.064201738434421</v>
+        <v>0.60108028088263</v>
       </c>
       <c r="W44">
-        <v>0.60108028088263</v>
-      </c>
-      <c r="X44">
         <v>0.3390104510278449</v>
       </c>
     </row>
